--- a/arquivos/REM22062023_CARRO.xlsx
+++ b/arquivos/REM22062023_CARRO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\GIT - Pessoal\File Management\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FD11A1-C4E9-4377-9DD8-B75ADD7511EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C450CB7D-BAB5-4788-87BC-622D343B52C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
   <si>
     <t>Jose</t>
   </si>
@@ -47,6 +47,33 @@
   </si>
   <si>
     <t>Value</t>
+  </si>
+  <si>
+    <t>Chevrolet</t>
+  </si>
+  <si>
+    <t>BMW</t>
+  </si>
+  <si>
+    <t>Volkswagen</t>
+  </si>
+  <si>
+    <t>Honda</t>
+  </si>
+  <si>
+    <t>Ford</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Lucas</t>
   </si>
 </sst>
 </file>
@@ -866,7 +893,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -916,10 +943,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>120644</v>
@@ -930,10 +957,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>143066</v>
@@ -945,10 +972,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>165488</v>
@@ -959,10 +986,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>187910</v>
@@ -976,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>210332</v>
@@ -990,7 +1017,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>232754</v>
@@ -1001,10 +1028,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>255176</v>
@@ -1015,10 +1042,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>277598</v>
@@ -1029,10 +1056,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>300020</v>
@@ -1043,10 +1070,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D13">
         <v>322442</v>
@@ -1060,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <v>344864</v>
@@ -1074,7 +1101,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D15">
         <v>367286</v>
@@ -1085,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
         <v>1</v>
@@ -1099,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -1113,10 +1140,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>434552</v>
@@ -1127,10 +1154,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>456974</v>
@@ -1144,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D20">
         <v>479396</v>
@@ -1158,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D21">
         <v>501818</v>
@@ -1169,10 +1196,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D22">
         <v>524240</v>
